--- a/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
   <si>
     <t>CCSI</t>
   </si>
@@ -656,79 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -741,50 +741,53 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E8" s="3">
         <v>90600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>92800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>91500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>82400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>91800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>91100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>89300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>352700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>182100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>346800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>678500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>336800</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -797,50 +800,53 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E9" s="3">
         <v>16900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>15800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>58000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>40700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>75200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>154300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>77800</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -853,50 +859,53 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E10" s="3">
         <v>73700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>75600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>74000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>66600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>76400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>75500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>74200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>294700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>141400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>271600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>524300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>259000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -909,8 +918,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,50 +943,51 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11600</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,8 +1000,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,8 +1059,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1072,20 +1091,20 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>24600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>29800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-17100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1099,8 +1118,11 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1128,21 +1150,21 @@
       <c r="K15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3">
         <v>12300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>22300</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3">
         <v>28700</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1155,8 +1177,11 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,50 +1199,51 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E17" s="3">
         <v>51600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>54000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>57500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>45400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>59100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>50500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>50600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>177500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>149200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>258500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>424600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>219000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,50 +1256,53 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E18" s="3">
         <v>39000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>38900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>34000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>37000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>32700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>40600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>38700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>175200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>32900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>88300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>253900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>117800</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1286,8 +1315,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,50 +1340,51 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E20" s="3">
         <v>5200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
       </c>
       <c r="L20" s="3">
+        <v>200</v>
+      </c>
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-45800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-19100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1364,50 +1397,53 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E21" s="3">
         <v>48500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>44400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>37500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>34700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>39400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>46000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>42500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>227200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>49800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>121400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>287800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>136500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1420,38 +1456,41 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E22" s="3">
         <v>12600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14300</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1467,8 +1506,8 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1476,50 +1515,53 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E23" s="3">
         <v>31500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>27300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>20600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>29800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>25600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>161100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>33700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>88700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>208000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>98700</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1532,50 +1574,53 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E24" s="3">
         <v>7500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>39900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>13800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>55100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>24300</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1588,8 +1633,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,50 +1692,53 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E26" s="3">
         <v>24000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>121200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>27200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>74900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>152900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>74400</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1700,50 +1751,53 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E27" s="3">
         <v>24000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>121200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>27200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>74900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>152900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>74400</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1756,8 +1810,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,13 +1869,16 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>3</v>
@@ -1826,8 +1886,8 @@
       <c r="F29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -1839,11 +1899,11 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-12200</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1859,8 +1919,8 @@
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -1868,8 +1928,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1987,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,50 +2046,53 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
       </c>
       <c r="L32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>45800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>19100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2036,50 +2105,53 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E33" s="3">
         <v>24000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>109000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>27200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>74900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>152900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>74400</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2092,8 +2164,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,50 +2223,53 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E35" s="3">
         <v>24000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>109000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>27200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>74900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>152900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>74400</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2204,55 +2282,58 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2265,8 +2346,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2371,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,47 +2394,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E41" s="3">
         <v>155700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>112000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>111300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>94200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>103700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>76300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>93900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>297800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>192600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>128200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,8 +2451,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2421,47 +2510,50 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E43" s="3">
         <v>29700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>30800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>29600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>28000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>31100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>29900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>24800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>37600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>41300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>42200</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2477,8 +2569,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2533,47 +2628,50 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E45" s="3">
         <v>7200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>4900</v>
       </c>
       <c r="I45" s="3">
         <v>4900</v>
       </c>
       <c r="J45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K45" s="3">
         <v>5400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>31900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27800</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,47 +2687,50 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E46" s="3">
         <v>192600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>155800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>155500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>136500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>139700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>111100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>128100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>96300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>367300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>268500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>198300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,8 +2746,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2671,21 +2775,21 @@
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>8800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8800</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,47 +2805,50 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E48" s="3">
         <v>82300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>75500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>68900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>62800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>54900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>50400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>46500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>101900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>101200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>115000</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2757,47 +2864,50 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>393800</v>
+      </c>
+      <c r="E49" s="3">
         <v>392100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>394900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>395800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>395700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>391000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>399800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>397000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>382800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1047800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1062700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1110400</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,8 +2923,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2982,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,47 +3041,50 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E52" s="3">
         <v>39600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>40800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>43000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>38800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>41000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>42700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>43800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>42700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>51000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>145500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>58900</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,8 +3100,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,47 +3159,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>647300</v>
+      </c>
+      <c r="E54" s="3">
         <v>706500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>667100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>663300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>633900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>626600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>604000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>615300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>562800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1576800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1586900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1491400</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3218,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3243,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,47 +3266,48 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E57" s="3">
         <v>52900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>35500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>54300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>61700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>39500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>56600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>40200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>65000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>61800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>81000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,31 +3323,34 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>8600</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3249,47 +3382,50 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E59" s="3">
         <v>32200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>29400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>31100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>30100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>33900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>42700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>53500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>37800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>112800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>121800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>123600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,47 +3441,50 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E60" s="3">
         <v>85100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>65000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>85500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>71300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>95600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>82200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>110100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>78000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>177800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>183500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>204700</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,38 +3500,41 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>725400</v>
+      </c>
+      <c r="E61" s="3">
         <v>795300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>794800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>794300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>793900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>793400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>792900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>792500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>792000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3417,47 +3559,50 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E62" s="3">
         <v>25400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>29900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>28200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>162300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>169600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>164200</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3618,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3677,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3736,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,47 +3795,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>823400</v>
+      </c>
+      <c r="E66" s="3">
         <v>905800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>884500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>904000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>889200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>918900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>903200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>929300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>895500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>340100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>353100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>368900</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +3854,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3879,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3936,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3995,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,8 +4054,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,38 +4113,41 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-173100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-189900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-213900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-235000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-250400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-267000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-280400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-302100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-318900</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3990,8 +4163,8 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S72" s="3">
         <v>0</v>
@@ -3999,8 +4172,11 @@
       <c r="T72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4231,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4290,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,47 +4349,50 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-176100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-199300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-217400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-240700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-255300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-292300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-299200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-313900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-332700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1236700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1233700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1122500</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4408,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,55 +4467,58 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4340,50 +4531,53 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E81" s="3">
         <v>24000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>109000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>27200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>74900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>152900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>74400</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,8 +4590,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,8 +4615,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4427,41 +4625,41 @@
         <v>4400</v>
       </c>
       <c r="E83" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="F83" s="3">
         <v>4300</v>
       </c>
       <c r="G83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H83" s="3">
         <v>3900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>51800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>16100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>32700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>79800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>37800</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4474,8 +4672,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4731,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4790,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4849,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4908,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,50 +4967,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E89" s="3">
         <v>60000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>37100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>49900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>233700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>69800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>126600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>238800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>120200</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4810,8 +5026,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,50 +5051,51 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-10100</v>
+        <v>-7700</v>
       </c>
       <c r="E91" s="3">
         <v>-10100</v>
       </c>
       <c r="F91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-8500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-32500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-21100</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4888,8 +5108,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5167,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,50 +5226,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-10100</v>
+        <v>-7700</v>
       </c>
       <c r="E94" s="3">
         <v>-10100</v>
       </c>
       <c r="F94" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="G94" s="3">
         <v>-12500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-20800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-42500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>43000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-80800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-60900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-39300</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5056,8 +5285,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5310,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5134,8 +5367,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5426,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5485,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,50 +5544,53 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-67600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-247800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>18800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-179100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-46300</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,50 +5603,53 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>6600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5414,50 +5662,53 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E102" s="3">
         <v>43700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>27400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>27100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-61400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>105200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>64400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>33900</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,6 +5719,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
   <si>
     <t>CCSI</t>
   </si>
@@ -656,82 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -744,53 +745,56 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>88100</v>
+      </c>
+      <c r="E8" s="3">
         <v>87800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>90600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>92800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>91500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>82400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>91800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>91100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>89300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>352700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>182100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>346800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>678500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>336800</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,53 +807,56 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E9" s="3">
         <v>16700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>58000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>40700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>75200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>154300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>77800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -862,8 +869,11 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -871,44 +881,44 @@
         <v>71100</v>
       </c>
       <c r="E10" s="3">
+        <v>71100</v>
+      </c>
+      <c r="F10" s="3">
         <v>73700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>75600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>74000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>66600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>76400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>75500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>74200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>294700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>141400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>271600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>524300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>259000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,8 +931,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -944,53 +957,54 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
         <v>2400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>22800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11600</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1003,8 +1017,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1062,8 +1079,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1094,20 +1114,20 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>24600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>29800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-17100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
@@ -1121,8 +1141,11 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1153,21 +1176,21 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3">
         <v>12300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>22300</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3">
         <v>28700</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,8 +1203,11 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1200,53 +1226,54 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E17" s="3">
         <v>52300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>51600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>54000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>57500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>45400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>59100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>50500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>50600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>177500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>149200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>258500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>424600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>219000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,53 +1286,56 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E18" s="3">
         <v>35500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>38900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>34000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>37000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>32700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>40600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>38700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>175200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>32900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>88300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>253900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>117800</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1348,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1341,53 +1374,54 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1600</v>
-      </c>
-      <c r="K20" s="3">
-        <v>200</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
       <c r="M20" s="3">
+        <v>200</v>
+      </c>
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-45800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1400,53 +1434,56 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E21" s="3">
         <v>35500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>48500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>44400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>37500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>34700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>39400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>46000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>42500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>227200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>49800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>121400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>287800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>136500</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,41 +1496,44 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E22" s="3">
         <v>7400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14300</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1509,8 +1549,8 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1518,53 +1558,56 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E23" s="3">
         <v>23800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>31500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>27300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>20600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>25600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>161100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>33700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>88700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>208000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>98700</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,53 +1620,56 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E24" s="3">
         <v>7000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>39900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>13800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>55100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>24300</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1636,8 +1682,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1695,53 +1744,56 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E26" s="3">
         <v>16800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>24000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>21100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>21900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>121200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>74900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>152900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>74400</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,53 +1806,56 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E27" s="3">
         <v>16800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>24000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>15400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>21900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>121200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>74900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>152900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>74400</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1813,8 +1868,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1872,16 +1930,19 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>3</v>
@@ -1889,8 +1950,8 @@
       <c r="G29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -1902,11 +1963,11 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-12200</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1922,8 +1983,8 @@
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -1931,8 +1992,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1990,8 +2054,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2049,53 +2116,56 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E32" s="3">
         <v>4400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-200</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
       <c r="M32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>45800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>19100</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2108,53 +2178,56 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E33" s="3">
         <v>16800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>24000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>21900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>109000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>74900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>152900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>74400</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,8 +2240,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2226,53 +2302,56 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E35" s="3">
         <v>16800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>24000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>21900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>109000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>74900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>152900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>74400</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,58 +2364,61 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2349,8 +2431,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2372,8 +2457,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2395,50 +2481,51 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E41" s="3">
         <v>88700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>155700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>112000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>111300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>94200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>103700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>76300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>93900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>66800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>297800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>192600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>128200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2454,8 +2541,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2513,50 +2603,53 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E43" s="3">
         <v>26300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>30800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>29600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>28000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>31100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>28800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>24800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>37600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>41300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>42200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,8 +2665,11 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2631,50 +2727,53 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E45" s="3">
         <v>10200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>4900</v>
       </c>
       <c r="J45" s="3">
         <v>4900</v>
       </c>
       <c r="K45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L45" s="3">
         <v>5400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>31900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27800</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,50 +2789,53 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E46" s="3">
         <v>125200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>192600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>155800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>155500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>136500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>139700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>111100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>128100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>96300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>367300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>268500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>198300</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,8 +2851,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2778,21 +2883,21 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>8800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8800</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2808,50 +2913,53 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>93100</v>
+      </c>
+      <c r="E48" s="3">
         <v>88000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>82300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>75500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>68900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>62800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>50400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>46500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>101900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>101200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>115000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2867,50 +2975,53 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>391200</v>
+      </c>
+      <c r="E49" s="3">
         <v>393800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>392100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>394900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>395800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>395700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>391000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>399800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>397000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>382800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1047800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1062700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1110400</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,8 +3037,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2985,8 +3099,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3044,50 +3161,53 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E52" s="3">
         <v>40200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>40800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>43000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>38800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>41000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>42700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>43800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>51000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>145500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>58900</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3103,8 +3223,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3162,50 +3285,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>620800</v>
+      </c>
+      <c r="E54" s="3">
         <v>647300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>706500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>667100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>663300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>633900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>626600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>604000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>615300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>562800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1576800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1586900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1491400</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,8 +3347,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3244,8 +3373,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3267,50 +3397,51 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E57" s="3">
         <v>36400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>52900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>35500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>54300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>61700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>39500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>56600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>40200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>65000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>61800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>81000</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,17 +3457,20 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>8600</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3486,8 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3385,50 +3519,53 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E59" s="3">
         <v>26400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>32200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>31100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>30100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>33900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>42700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>53500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>37800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>112800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>121800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>123600</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,50 +3581,53 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E60" s="3">
         <v>71400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>85100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>65000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>85500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>71300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>95600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>82200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>110100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>78000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>177800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>183500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>204700</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3503,41 +3643,44 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>671700</v>
+      </c>
+      <c r="E61" s="3">
         <v>725400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>795300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>794800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>794300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>793900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>793400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>792900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>792500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>792000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3562,50 +3705,53 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E62" s="3">
         <v>26600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>25400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>24000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>28200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>162300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>169600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>164200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,8 +3767,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3680,8 +3829,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3739,8 +3891,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3798,50 +3953,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>772600</v>
+      </c>
+      <c r="E66" s="3">
         <v>823400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>905800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>884500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>904000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>889200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>918900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>903200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>929300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>895500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>340100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>353100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>368900</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,8 +4015,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3880,8 +4041,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3939,8 +4101,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3998,8 +4163,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4057,8 +4225,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4116,41 +4287,44 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-146700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-173100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-189900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-213900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-235000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-250400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-267000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-280400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-302100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-318900</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4166,8 +4340,8 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T72" s="3">
         <v>0</v>
@@ -4175,8 +4349,11 @@
       <c r="U72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4234,8 +4411,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4293,8 +4473,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4352,50 +4535,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-151800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-176100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-199300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-217400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-240700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-255300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-292300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-299200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-313900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-332700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1236700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1233700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1122500</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4411,8 +4597,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4470,58 +4659,61 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4534,53 +4726,56 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E81" s="3">
         <v>16800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>24000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>21900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>109000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>74900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>152900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>74400</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4593,8 +4788,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4616,53 +4814,54 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4400</v>
+        <v>4800</v>
       </c>
       <c r="E83" s="3">
         <v>4400</v>
       </c>
       <c r="F83" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="G83" s="3">
         <v>4300</v>
       </c>
       <c r="H83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I83" s="3">
         <v>3900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>51800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>16100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>79800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>37800</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4675,8 +4874,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4734,8 +4936,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4793,8 +4998,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4852,8 +5060,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4911,8 +5122,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4970,53 +5184,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E89" s="3">
         <v>2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>60000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>37100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>49900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>233700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>69800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>126600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>238800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>120200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5029,8 +5246,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5052,53 +5272,54 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7700</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-10100</v>
       </c>
       <c r="F91" s="3">
         <v>-10100</v>
       </c>
       <c r="G91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-8500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5111,8 +5332,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5170,8 +5394,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5229,53 +5456,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7700</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-10100</v>
       </c>
       <c r="F94" s="3">
         <v>-10100</v>
       </c>
       <c r="G94" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="H94" s="3">
         <v>-12500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-42500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>43000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-80800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-60900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-39300</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5288,8 +5518,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5311,8 +5544,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5370,8 +5604,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5429,8 +5666,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5488,8 +5728,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5547,53 +5790,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-58800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-67600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-247800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>18800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-179100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-46300</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5606,53 +5852,56 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E101" s="3">
         <v>6300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>6600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5665,53 +5914,56 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-67000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>43700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>17100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>27400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>27100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-61400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>105200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>64400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>5400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>33900</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5722,6 +5974,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
   <si>
     <t>CCSI</t>
   </si>
@@ -656,86 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -748,56 +749,59 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>87500</v>
+      </c>
+      <c r="E8" s="3">
         <v>88100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>87800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>90600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>92800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>91500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>82400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>91800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>91100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>89300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>352700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>182100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>346800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>678500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>336800</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,56 +814,59 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E9" s="3">
         <v>17000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>58000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>40700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>75200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>154300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>77800</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,56 +879,59 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>71100</v>
+        <v>70400</v>
       </c>
       <c r="E10" s="3">
         <v>71100</v>
       </c>
       <c r="F10" s="3">
+        <v>71100</v>
+      </c>
+      <c r="G10" s="3">
         <v>73700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>75600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>74000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>66600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>76400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>75500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>74200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>294700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>141400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>271600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>524300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>259000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -934,8 +944,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -958,56 +971,57 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E12" s="3">
         <v>1900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>22800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11600</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1020,8 +1034,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1082,16 +1099,19 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-4900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1117,20 +1137,20 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>24600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>29800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1144,8 +1164,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1179,21 +1202,21 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3">
         <v>12300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>22300</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3">
         <v>28700</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1206,8 +1229,11 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1227,56 +1253,57 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>45600</v>
+      </c>
+      <c r="F17" s="3">
+        <v>52300</v>
+      </c>
+      <c r="G17" s="3">
+        <v>51600</v>
+      </c>
+      <c r="H17" s="3">
+        <v>54000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>57500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>45400</v>
+      </c>
+      <c r="K17" s="3">
+        <v>59100</v>
+      </c>
+      <c r="L17" s="3">
         <v>50500</v>
       </c>
-      <c r="E17" s="3">
-        <v>52300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>51600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>54000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>57500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>45400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>59100</v>
-      </c>
-      <c r="K17" s="3">
-        <v>50500</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>50600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>177500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>149200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>258500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>424600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>219000</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1289,56 +1316,59 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>37600</v>
+        <v>41600</v>
       </c>
       <c r="E18" s="3">
+        <v>42500</v>
+      </c>
+      <c r="F18" s="3">
         <v>35500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>39000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>38900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>34000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>37000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>32700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>40600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>38700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>175200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>88300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>253900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>117800</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1351,8 +1381,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1375,56 +1408,57 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E20" s="3">
         <v>4900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>200</v>
       </c>
       <c r="M20" s="3">
         <v>200</v>
       </c>
       <c r="N20" s="3">
+        <v>200</v>
+      </c>
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-19100</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1437,56 +1471,59 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>47300</v>
+        <v>48000</v>
       </c>
       <c r="E21" s="3">
+        <v>52200</v>
+      </c>
+      <c r="F21" s="3">
         <v>35500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>48500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>44400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>37500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>34700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>39400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>46000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>42500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>227200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>49800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>121400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>287800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>136500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1499,44 +1536,47 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>6200</v>
+        <v>10400</v>
       </c>
       <c r="E22" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F22" s="3">
         <v>7400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14300</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1552,8 +1592,8 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1561,56 +1601,59 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E23" s="3">
         <v>36300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>23800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>31500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>27300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>20600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>29800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>25600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>161100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>33700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>88700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>208000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>98700</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1623,56 +1666,59 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E24" s="3">
         <v>9900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>39900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>55100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>24300</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1685,8 +1731,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1747,56 +1796,59 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E26" s="3">
         <v>26400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>21900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>121200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>27200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>74900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>152900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>74400</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,56 +1861,59 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E27" s="3">
         <v>26400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>24000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>21900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>18500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>121200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>27200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>74900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>152900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>74400</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1871,8 +1926,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1933,19 +1991,22 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>3</v>
@@ -1953,8 +2014,8 @@
       <c r="H29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -1966,11 +2027,11 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-12200</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,8 +2047,8 @@
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -1995,8 +2056,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2057,8 +2121,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2119,56 +2186,59 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-200</v>
       </c>
       <c r="M32" s="3">
         <v>-200</v>
       </c>
       <c r="N32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>45800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>19100</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2181,56 +2251,59 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E33" s="3">
         <v>26400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>24000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>21900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>18500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>109000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>27200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>74900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>152900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>74400</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2243,8 +2316,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2305,56 +2381,59 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E35" s="3">
         <v>26400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>24000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>21900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>18500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>109000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>27200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>74900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>152900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>74400</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,61 +2446,64 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2434,8 +2516,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2458,8 +2543,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2482,53 +2568,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E41" s="3">
         <v>61500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>88700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>155700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>112000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>111300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>94200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>103700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>76300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>93900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>66800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>297800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>192600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>128200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2544,8 +2631,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2606,53 +2696,56 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E43" s="3">
         <v>27400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>29700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>30800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>28000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>31100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>28800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>37600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>41300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>42200</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2668,8 +2761,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2730,53 +2826,56 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E45" s="3">
         <v>9800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>4900</v>
       </c>
       <c r="K45" s="3">
         <v>4900</v>
       </c>
       <c r="L45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M45" s="3">
         <v>5400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>31900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27800</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,53 +2891,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E46" s="3">
         <v>98700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>125200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>192600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>155800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>155500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>136500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>139700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>111100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>128100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>96300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>367300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>268500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>198300</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2854,8 +2956,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2886,21 +2991,21 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>8800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8800</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2916,53 +3021,56 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E48" s="3">
         <v>93100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>88000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>82300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>75500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>68900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>62800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>50400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>46500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>101900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>101200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>115000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,53 +3086,56 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>389800</v>
+      </c>
+      <c r="E49" s="3">
         <v>391200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>393800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>392100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>394900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>395800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>395700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>391000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>399800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>397000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>382800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1047800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1062700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1110400</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3040,8 +3151,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3102,8 +3216,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3164,53 +3281,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E52" s="3">
         <v>37700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>40200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>40800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>43000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>38800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>41000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>42700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>43800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>51000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>145500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>58900</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3226,8 +3346,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3288,53 +3411,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>608500</v>
+      </c>
+      <c r="E54" s="3">
         <v>620800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>647300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>706500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>667100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>663300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>633900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>626600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>604000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>615300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>562800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1576800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1586900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1491400</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3476,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3374,8 +3503,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3398,53 +3528,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E57" s="3">
         <v>8200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>52900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>35500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>54300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>61700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>39500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>56600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>40200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>65000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>61800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>81000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3460,20 +3591,23 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>16600</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>8600</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3489,8 +3623,8 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3522,53 +3656,56 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E59" s="3">
         <v>66000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>32200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>31100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>30100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>33900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>42700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>53500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>37800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>112800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>121800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>123600</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3584,53 +3721,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E60" s="3">
         <v>74200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>71400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>85100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>65000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>85500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>71300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>95600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>82200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>110100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>78000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>177800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>183500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>204700</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,44 +3786,47 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>626200</v>
+      </c>
+      <c r="E61" s="3">
         <v>671700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>725400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>795300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>794800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>794300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>793900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>793400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>792900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>792500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>792000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3708,53 +3851,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E62" s="3">
         <v>26700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>24200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>26700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>25500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>162300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>169600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>164200</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3770,8 +3916,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3832,8 +3981,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3894,8 +4046,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3956,53 +4111,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>732900</v>
+      </c>
+      <c r="E66" s="3">
         <v>772600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>823400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>905800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>884500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>904000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>889200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>918900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>903200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>929300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>895500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>340100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>353100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>368900</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4018,8 +4176,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4042,8 +4203,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4104,8 +4266,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4166,8 +4331,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4228,8 +4396,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4290,44 +4461,47 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-122900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-146700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-173100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-189900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-213900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-235000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-250400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-267000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-280400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-302100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-318900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4343,8 +4517,8 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U72" s="3">
         <v>0</v>
@@ -4352,8 +4526,11 @@
       <c r="V72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4414,8 +4591,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4476,8 +4656,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4538,53 +4721,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-124400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-151800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-176100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-199300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-217400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-240700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-255300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-292300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-299200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-313900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-332700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1236700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1233700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1122500</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4600,8 +4786,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4662,61 +4851,64 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4729,56 +4921,59 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E81" s="3">
         <v>26400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>24000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>21900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>18500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>109000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>27200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>74900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>152900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>74400</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,8 +4986,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4815,56 +5013,57 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E83" s="3">
         <v>4800</v>
-      </c>
-      <c r="E83" s="3">
-        <v>4400</v>
       </c>
       <c r="F83" s="3">
         <v>4400</v>
       </c>
       <c r="G83" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="H83" s="3">
         <v>4300</v>
       </c>
       <c r="I83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J83" s="3">
         <v>3900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>51800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>16100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>32700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>79800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>37800</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4877,8 +5076,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4939,8 +5141,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5001,8 +5206,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5063,8 +5271,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5125,8 +5336,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5187,56 +5401,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E89" s="3">
         <v>44700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>60000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>38000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>37100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>49900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>233700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>69800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>126600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>238800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>120200</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5249,8 +5466,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5273,56 +5493,57 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7700</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-10100</v>
       </c>
       <c r="G91" s="3">
         <v>-10100</v>
       </c>
       <c r="H91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-8500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-32500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-21100</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5335,8 +5556,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5397,8 +5621,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5459,56 +5686,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7700</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-10100</v>
       </c>
       <c r="G94" s="3">
         <v>-10100</v>
       </c>
       <c r="H94" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="I94" s="3">
         <v>-12500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-20800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-42500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>43000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-80800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-60900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-39300</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5521,8 +5751,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5545,8 +5778,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5607,8 +5841,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5669,8 +5906,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5731,8 +5971,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5793,56 +6036,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-58800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-67600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-247800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>18800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-179100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-46300</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5855,56 +6101,59 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>7300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>6600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5917,56 +6166,59 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-27200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-67000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>43700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>27400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>27100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-61400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>105200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>64400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>33900</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5977,6 +6229,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>CCSI</t>
   </si>
@@ -656,90 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,59 +753,62 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E8" s="3">
         <v>87500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>88100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>87800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>90600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>92800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>91500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>82400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>91800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>91100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>89300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>352700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>182100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>346800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>678500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>336800</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -817,59 +821,62 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E9" s="3">
         <v>17100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>58000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>40700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>75200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>154300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>77800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,59 +889,62 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E10" s="3">
         <v>70400</v>
-      </c>
-      <c r="E10" s="3">
-        <v>71100</v>
       </c>
       <c r="F10" s="3">
         <v>71100</v>
       </c>
       <c r="G10" s="3">
+        <v>71000</v>
+      </c>
+      <c r="H10" s="3">
         <v>73700</v>
       </c>
-      <c r="H10" s="3">
-        <v>75600</v>
-      </c>
       <c r="I10" s="3">
-        <v>74000</v>
+        <v>75500</v>
       </c>
       <c r="J10" s="3">
+        <v>73900</v>
+      </c>
+      <c r="K10" s="3">
         <v>66600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>76400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>75500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>74200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>294700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>141400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>271600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>524300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>259000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -947,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,59 +985,60 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>22800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11600</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,16 +1119,19 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-4900</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1140,20 +1160,20 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>24600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>29800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-17100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
@@ -1167,31 +1187,34 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="G15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I15" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J15" s="3">
+        <v>4300</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1205,21 +1228,21 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3">
         <v>12300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>22300</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3">
         <v>28700</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1232,8 +1255,11 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,59 +1280,60 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>45900</v>
+        <v>49300</v>
       </c>
       <c r="E17" s="3">
-        <v>45600</v>
+        <v>47600</v>
       </c>
       <c r="F17" s="3">
+        <v>50500</v>
+      </c>
+      <c r="G17" s="3">
         <v>52300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>51600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>54000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>57500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>45400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>59100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>50500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>50600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>177500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>149200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>258500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>424600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>219000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,59 +1346,62 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>41600</v>
+        <v>38400</v>
       </c>
       <c r="E18" s="3">
-        <v>42500</v>
+        <v>39900</v>
       </c>
       <c r="F18" s="3">
+        <v>37700</v>
+      </c>
+      <c r="G18" s="3">
         <v>35500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>39000</v>
       </c>
       <c r="H18" s="3">
         <v>38900</v>
       </c>
       <c r="I18" s="3">
+        <v>38800</v>
+      </c>
+      <c r="J18" s="3">
         <v>34000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>37000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>32700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>40600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>38700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>175200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>32900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>88300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>253900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>117800</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,59 +1442,60 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1300</v>
+        <v>2100</v>
       </c>
       <c r="E20" s="3">
-        <v>4900</v>
+        <v>-700</v>
       </c>
       <c r="F20" s="3">
-        <v>-4400</v>
+        <v>-3900</v>
       </c>
       <c r="G20" s="3">
-        <v>5200</v>
+        <v>5900</v>
       </c>
       <c r="H20" s="3">
-        <v>1200</v>
+        <v>-3700</v>
       </c>
       <c r="I20" s="3">
-        <v>-900</v>
+        <v>-600</v>
       </c>
       <c r="J20" s="3">
+        <v>800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-6300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1600</v>
-      </c>
-      <c r="M20" s="3">
-        <v>200</v>
       </c>
       <c r="N20" s="3">
         <v>200</v>
       </c>
       <c r="O20" s="3">
+        <v>200</v>
+      </c>
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-45800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-19100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,59 +1508,62 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>48000</v>
+        <v>41400</v>
       </c>
       <c r="E21" s="3">
-        <v>52200</v>
+        <v>45700</v>
       </c>
       <c r="F21" s="3">
-        <v>35500</v>
+        <v>46300</v>
       </c>
       <c r="G21" s="3">
-        <v>48500</v>
+        <v>34000</v>
       </c>
       <c r="H21" s="3">
-        <v>44400</v>
+        <v>47000</v>
       </c>
       <c r="I21" s="3">
+        <v>43800</v>
+      </c>
+      <c r="J21" s="3">
         <v>37500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>34700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>39400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>46000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>42500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>227200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>49800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>121400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>287800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>136500</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,47 +1576,50 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>10400</v>
+        <v>9800</v>
       </c>
       <c r="E22" s="3">
-        <v>11100</v>
+        <v>8700</v>
       </c>
       <c r="F22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="G22" s="3">
         <v>7400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14300</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1595,8 +1635,8 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1604,59 +1644,62 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E23" s="3">
         <v>32500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>36300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>23800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>31500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>27300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>20600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>18900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>29800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>161100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>33700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>88700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>208000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>98700</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1669,59 +1712,62 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E24" s="3">
         <v>8600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>39900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>55100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>24300</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,8 +1780,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,59 +1848,62 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E26" s="3">
         <v>23900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>26400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>24000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>15500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>121200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>74900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>152900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>74400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,59 +1916,62 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E27" s="3">
         <v>23900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>26400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>24000</v>
       </c>
-      <c r="H27" s="3">
-        <v>21100</v>
-      </c>
       <c r="I27" s="3">
-        <v>15500</v>
+        <v>21000</v>
       </c>
       <c r="J27" s="3">
+        <v>15400</v>
+      </c>
+      <c r="K27" s="3">
         <v>14600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>15400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>21900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>18500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>121200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>27200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>74900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>152900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>74400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1929,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,28 +2052,31 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2030,11 +2091,11 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-12200</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2050,8 +2111,8 @@
       <c r="T29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2059,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,59 +2256,62 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1300</v>
+        <v>-2100</v>
       </c>
       <c r="E32" s="3">
-        <v>-4900</v>
+        <v>700</v>
       </c>
       <c r="F32" s="3">
-        <v>4400</v>
+        <v>3900</v>
       </c>
       <c r="G32" s="3">
-        <v>-5200</v>
+        <v>-5900</v>
       </c>
       <c r="H32" s="3">
-        <v>-1200</v>
+        <v>3700</v>
       </c>
       <c r="I32" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="J32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K32" s="3">
         <v>6300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-200</v>
       </c>
       <c r="N32" s="3">
         <v>-200</v>
       </c>
       <c r="O32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>45800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>19100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,59 +2324,62 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E33" s="3">
         <v>23900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>26400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>24000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>15500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>21900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>18500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>109000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>74900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>152900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>74400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,59 +2460,62 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E35" s="3">
         <v>23900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>26400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>24000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>15500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>21900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>18500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>109000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>74900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>152900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>74400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,64 +2528,67 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2601,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,56 +2655,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E41" s="3">
         <v>49200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>61500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>88700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>155700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>112000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>111300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>94200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>103700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>76300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>93900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>66800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>297800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>192600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>128200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2634,8 +2721,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2699,56 +2789,59 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E43" s="3">
         <v>26100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>29700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>30800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>29600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>28000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>31100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>24800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>37600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>41300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>42200</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2764,31 +2857,34 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2829,56 +2925,59 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8600</v>
+        <v>6600</v>
       </c>
       <c r="E45" s="3">
-        <v>9800</v>
+        <v>5100</v>
       </c>
       <c r="F45" s="3">
-        <v>10200</v>
+        <v>6800</v>
       </c>
       <c r="G45" s="3">
-        <v>7200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>13000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>14600</v>
-      </c>
-      <c r="J45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>14300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>4900</v>
       </c>
       <c r="L45" s="3">
         <v>4900</v>
       </c>
       <c r="M45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N45" s="3">
         <v>5400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>31900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>34600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27800</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,56 +2993,59 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E46" s="3">
         <v>84000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>98700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>125200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>192600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>155800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>155500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>136500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>139700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>111100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>128100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>96300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>367300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>268500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>198300</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,31 +3061,34 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>4000</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2994,21 +3099,21 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>8800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8800</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,56 +3129,59 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>103300</v>
+      </c>
+      <c r="E48" s="3">
         <v>98000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>93100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>88000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>82300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>75500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>68900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>62800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>54900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>50400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>46500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>41100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>101900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>101200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>115000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3089,56 +3197,59 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>391700</v>
+      </c>
+      <c r="E49" s="3">
         <v>389800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>391200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>393800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>392100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>394900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>395800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>395700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>391000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>399800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>397000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>382800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1047800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1062700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1110400</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3154,8 +3265,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,56 +3401,59 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>36700</v>
+        <v>4400</v>
       </c>
       <c r="E52" s="3">
-        <v>37700</v>
+        <v>4600</v>
       </c>
       <c r="F52" s="3">
-        <v>40200</v>
+        <v>5000</v>
       </c>
       <c r="G52" s="3">
-        <v>39600</v>
+        <v>1400</v>
       </c>
       <c r="H52" s="3">
-        <v>40800</v>
+        <v>5600</v>
       </c>
       <c r="I52" s="3">
-        <v>43000</v>
+        <v>6000</v>
       </c>
       <c r="J52" s="3">
+        <v>6400</v>
+      </c>
+      <c r="K52" s="3">
         <v>38800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>41000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>43800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>42700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>51000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>145500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>58900</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3469,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,56 +3537,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>622500</v>
+      </c>
+      <c r="E54" s="3">
         <v>608500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>620800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>647300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>706500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>667100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>663300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>633900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>626600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>604000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>615300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>562800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1576800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1586900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1491400</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,56 +3659,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E57" s="3">
         <v>7800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8200</v>
       </c>
-      <c r="F57" s="3">
-        <v>36400</v>
-      </c>
       <c r="G57" s="3">
+        <v>9900</v>
+      </c>
+      <c r="H57" s="3">
         <v>52900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>35500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>54300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>61700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>39500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>56600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>40200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>65000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>61800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>81000</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,31 +3725,34 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16600</v>
+        <v>11700</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>18600</v>
       </c>
       <c r="F58" s="3">
-        <v>8600</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>2000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>10600</v>
+      </c>
+      <c r="H58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J58" s="3">
+        <v>2800</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -3626,8 +3760,8 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3659,56 +3793,59 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>56000</v>
+        <v>26200</v>
       </c>
       <c r="E59" s="3">
-        <v>66000</v>
+        <v>27000</v>
       </c>
       <c r="F59" s="3">
-        <v>26400</v>
+        <v>27000</v>
       </c>
       <c r="G59" s="3">
-        <v>32200</v>
+        <v>24300</v>
       </c>
       <c r="H59" s="3">
-        <v>29400</v>
+        <v>29300</v>
       </c>
       <c r="I59" s="3">
-        <v>31100</v>
+        <v>26500</v>
       </c>
       <c r="J59" s="3">
+        <v>28300</v>
+      </c>
+      <c r="K59" s="3">
         <v>30100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>33900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>53500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>37800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>112800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>121800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>123600</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,56 +3861,59 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>85300</v>
+      </c>
+      <c r="E60" s="3">
         <v>80400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>74200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>71400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>85100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>65000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>85500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>71300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>95600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>82200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>110100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>78000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>177800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>183500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>204700</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3789,47 +3929,50 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>626200</v>
+        <v>615700</v>
       </c>
       <c r="E61" s="3">
-        <v>671700</v>
+        <v>638400</v>
       </c>
       <c r="F61" s="3">
-        <v>725400</v>
+        <v>684400</v>
       </c>
       <c r="G61" s="3">
-        <v>795300</v>
+        <v>738600</v>
       </c>
       <c r="H61" s="3">
-        <v>794800</v>
+        <v>808200</v>
       </c>
       <c r="I61" s="3">
-        <v>794300</v>
+        <v>807900</v>
       </c>
       <c r="J61" s="3">
+        <v>807700</v>
+      </c>
+      <c r="K61" s="3">
         <v>793900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>793400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>792900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>792500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>792000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3854,56 +3997,59 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>26300</v>
+        <v>12100</v>
       </c>
       <c r="E62" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F62" s="3">
+        <v>10700</v>
+      </c>
+      <c r="G62" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H62" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I62" s="3">
+        <v>8500</v>
+      </c>
+      <c r="J62" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K62" s="3">
+        <v>24000</v>
+      </c>
+      <c r="L62" s="3">
+        <v>29900</v>
+      </c>
+      <c r="M62" s="3">
+        <v>28200</v>
+      </c>
+      <c r="N62" s="3">
         <v>26700</v>
       </c>
-      <c r="F62" s="3">
-        <v>26600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>25400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>24700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>24200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>24000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>29900</v>
-      </c>
-      <c r="L62" s="3">
-        <v>28200</v>
-      </c>
-      <c r="M62" s="3">
-        <v>26700</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>162300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>169600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>164200</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,56 +4269,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>715700</v>
+      </c>
+      <c r="E66" s="3">
         <v>732900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>772600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>823400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>905800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>884500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>904000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>889200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>918900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>903200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>929300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>895500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>340100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>353100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>368900</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,47 +4635,50 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-101700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-122900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-146700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-173100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-189900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-213900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-235000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-250400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-267000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-280400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-302100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-318900</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4520,8 +4694,8 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V72" s="3">
         <v>0</v>
@@ -4529,8 +4703,11 @@
       <c r="W72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,56 +4907,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-93200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-124400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-151800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-176100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-199300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-217400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-240700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-255300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-292300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-299200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-313900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-332700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1236700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1233700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1122500</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,64 +5043,67 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,59 +5116,62 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E81" s="3">
         <v>23900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>26400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>24000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>15500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>21900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>18500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>109000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>74900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>152900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>74400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4989,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,59 +5212,60 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5200</v>
+        <v>3400</v>
       </c>
       <c r="E83" s="3">
-        <v>4800</v>
+        <v>3200</v>
       </c>
       <c r="F83" s="3">
-        <v>4400</v>
+        <v>3200</v>
       </c>
       <c r="G83" s="3">
-        <v>4400</v>
+        <v>3000</v>
       </c>
       <c r="H83" s="3">
-        <v>4300</v>
+        <v>2600</v>
       </c>
       <c r="I83" s="3">
-        <v>4300</v>
+        <v>2800</v>
       </c>
       <c r="J83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K83" s="3">
         <v>3900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>51800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>16100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>32700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>79800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>37800</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5079,8 +5278,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,59 +5618,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E89" s="3">
         <v>24400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>44700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>60000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>38000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>37100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>49900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>233700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>69800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>126600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>238800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>120200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,59 +5714,60 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7700</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-10100</v>
       </c>
       <c r="H91" s="3">
         <v>-10100</v>
       </c>
       <c r="I91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-8500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-32500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-21100</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5559,8 +5780,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,59 +5916,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7700</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-10100</v>
       </c>
       <c r="H94" s="3">
         <v>-10100</v>
       </c>
       <c r="I94" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="J94" s="3">
         <v>-12500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-20800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-42500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>43000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-80800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-60900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-39300</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5754,8 +5984,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,31 +6012,32 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5844,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,59 +6282,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-27300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-58800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-67600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-247800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>18800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-179100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-46300</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6104,59 +6350,62 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-800</v>
+        <v>-3700</v>
       </c>
       <c r="E101" s="3">
-        <v>-4100</v>
+        <v>-1400</v>
       </c>
       <c r="F101" s="3">
-        <v>6300</v>
+        <v>1300</v>
       </c>
       <c r="G101" s="3">
-        <v>-3700</v>
+        <v>7300</v>
       </c>
       <c r="H101" s="3">
-        <v>-1400</v>
+        <v>-4400</v>
       </c>
       <c r="I101" s="3">
-        <v>1300</v>
+        <v>-4200</v>
       </c>
       <c r="J101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K101" s="3">
         <v>7300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>6600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6169,59 +6418,62 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-27200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-67000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>43700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-9500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>27400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>27100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-61400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>105200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>64400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>33900</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6232,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>CCSI</t>
   </si>
@@ -656,94 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -756,62 +756,65 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E8" s="3">
         <v>87800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>87500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>88100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>87800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>90600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>92800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>91500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>82400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>91800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>91100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>89300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>352700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>182100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>346800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>678500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>336800</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -824,62 +827,65 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E9" s="3">
         <v>17700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>58000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>40700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>75200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>154300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>77800</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -892,62 +898,65 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>69100</v>
+      </c>
+      <c r="E10" s="3">
         <v>70100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>70400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>71100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>71000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>73700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>75500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>73900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>66600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>76400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>75500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>74200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>294700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>141400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>271600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>524300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>259000</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -960,8 +969,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,62 +998,63 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E12" s="3">
         <v>2000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>22800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>11600</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,8 +1067,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,8 +1138,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1163,20 +1182,20 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>24600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>29800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-17100</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
@@ -1190,34 +1209,37 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E15" s="3">
         <v>5000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>4400</v>
       </c>
       <c r="H15" s="3">
         <v>4400</v>
       </c>
       <c r="I15" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="J15" s="3">
         <v>4300</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>4300</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
@@ -1231,21 +1253,21 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3">
         <v>12300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>22300</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" s="3">
         <v>28700</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1258,8 +1280,11 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,62 +1306,63 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E17" s="3">
         <v>49300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>47600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>50500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>52300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>51600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>54000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>57500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>45400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>59100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>50500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>50600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>177500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>149200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>258500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>424600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>219000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,62 +1375,65 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E18" s="3">
         <v>38400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>37700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>35500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>38900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>38800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>34000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>37000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>32700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>40600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>38700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>175200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>32900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>88300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>253900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>117800</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1417,8 +1446,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,62 +1475,63 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>2100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1600</v>
-      </c>
-      <c r="N20" s="3">
-        <v>200</v>
       </c>
       <c r="O20" s="3">
         <v>200</v>
       </c>
       <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-45800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-19100</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1511,62 +1544,65 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E21" s="3">
         <v>41400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>45700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>46300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>34000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>47000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>43800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>37500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>34700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>39400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>46000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>42500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>227200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>49800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>121400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>287800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>136500</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,50 +1615,53 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E22" s="3">
         <v>9800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14300</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1638,8 +1677,8 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1647,62 +1686,65 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E23" s="3">
         <v>27300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>36300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>31500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>27300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>20600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>29800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>25600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>161100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>33700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>88700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>208000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>98700</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1715,62 +1757,65 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E24" s="3">
         <v>6100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>39900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>13800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>55100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>24300</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1783,8 +1828,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,62 +1899,65 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E26" s="3">
         <v>21100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>26400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>24000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>15500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>15400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>121200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>74900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>152900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>74400</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1919,62 +1970,65 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E27" s="3">
         <v>21100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>23900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>26400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>15400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>15400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>121200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>74900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>152900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>74400</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1987,8 +2041,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2112,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2094,11 +2154,11 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-12200</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2114,8 +2174,8 @@
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2123,8 +2183,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2254,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,62 +2325,65 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-200</v>
       </c>
       <c r="O32" s="3">
         <v>-200</v>
       </c>
       <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>45800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>19100</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2327,62 +2396,65 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E33" s="3">
         <v>21100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>23900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>26400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>15500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>15400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>109000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>74900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>152900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>74400</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2395,8 +2467,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,62 +2538,65 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E35" s="3">
         <v>21100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>23900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>26400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>15500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>15400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>109000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>74900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>152900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>74400</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2531,67 +2609,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2604,8 +2685,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2714,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,59 +2741,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E41" s="3">
         <v>54600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>49200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>61500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>88700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>155700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>112000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>111300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>94200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>103700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>76300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>93900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>66800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>297800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>192600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>128200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,8 +2810,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2792,59 +2881,62 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E43" s="3">
         <v>25800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>26100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>30800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>28000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>31100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>28800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>37600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>41300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>42200</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +2952,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2886,8 +2981,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2928,25 +3023,28 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E45" s="3">
         <v>6600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6800</v>
       </c>
-      <c r="G45" s="3">
-        <v>4200</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>7500</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -2954,33 +3052,33 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>14300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>4900</v>
       </c>
       <c r="M45" s="3">
         <v>4900</v>
       </c>
       <c r="N45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="O45" s="3">
         <v>5400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>34600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27800</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,59 +3094,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E46" s="3">
         <v>89800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>84000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>98700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>125200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>192600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>155800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>155500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>136500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>139700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>111100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>128100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>96300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>367300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>268500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>198300</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,13 +3165,16 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>4000</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -3078,20 +3182,20 @@
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>4000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3102,21 +3206,21 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>8800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8800</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3132,59 +3236,62 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>106600</v>
+      </c>
+      <c r="E48" s="3">
         <v>103300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>98000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>93100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>88000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>82300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>75500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>68900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>62800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>54900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>50400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>46500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>41100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>101900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>101200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>115000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,59 +3307,62 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>386200</v>
+      </c>
+      <c r="E49" s="3">
         <v>391700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>389800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>391200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>393800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>392100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>394900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>395800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>395700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>391000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>399800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>397000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>382800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1047800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1062700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1110400</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3268,8 +3378,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3449,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,59 +3520,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>300</v>
+      </c>
+      <c r="E52" s="3">
         <v>4400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>41000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>43800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>42700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>51000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>145500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>58900</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3591,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,59 +3662,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>602200</v>
+      </c>
+      <c r="E54" s="3">
         <v>622500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>608500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>620800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>647300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>706500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>667100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>663300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>633900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>626600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>604000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>615300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>562800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1576800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1586900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1491400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3733,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3762,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,59 +3789,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E57" s="3">
         <v>9500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>52900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>35500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>54300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>61700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>39500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>56600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>40200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>65000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>61800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>81000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3728,43 +3858,46 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E58" s="3">
         <v>11700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10600</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2900</v>
       </c>
       <c r="I58" s="3">
         <v>2900</v>
       </c>
       <c r="J58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K58" s="3">
         <v>2800</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -3796,59 +3929,62 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E59" s="3">
         <v>26200</v>
-      </c>
-      <c r="E59" s="3">
-        <v>27000</v>
       </c>
       <c r="F59" s="3">
         <v>27000</v>
       </c>
       <c r="G59" s="3">
+        <v>27000</v>
+      </c>
+      <c r="H59" s="3">
         <v>24300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>28300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>30100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>33900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>42700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>53500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>37800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>112800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>121800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>123600</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,59 +4000,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E60" s="3">
         <v>85300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>80400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>74200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>71400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>85100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>65000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>85500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>71300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>95600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>82200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>110100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>78000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>177800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>183500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>204700</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,50 +4071,53 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>586100</v>
+      </c>
+      <c r="E61" s="3">
         <v>615700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>638400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>684400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>738600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>808200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>807900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>807700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>793900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>793400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>792900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>792500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>792000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4000,59 +4142,62 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E62" s="3">
         <v>12100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>28200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>25500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>162300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>169600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>164200</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,8 +4213,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4284,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4355,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,59 +4426,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>681700</v>
+      </c>
+      <c r="E66" s="3">
         <v>715700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>732900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>772600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>823400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>905800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>884500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>904000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>889200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>918900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>903200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>929300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>895500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>340100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>353100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>368900</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4497,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4526,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4595,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4666,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4570,8 +4737,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,50 +4808,53 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-83700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-101700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-122900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-146700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-173100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-189900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-213900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-235000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-250400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-267000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-280400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-302100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-318900</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4697,8 +4870,8 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -4706,8 +4879,11 @@
       <c r="X72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4950,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5021,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,59 +5092,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-93200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-124400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-151800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-176100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-199300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-217400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-240700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-255300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-292300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-299200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-313900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-332700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1236700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1233700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1122500</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4978,8 +5163,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,67 +5234,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5119,62 +5310,65 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E81" s="3">
         <v>21100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>23900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>26400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>15500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>15400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>109000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>74900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>152900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>74400</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5187,8 +5381,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,62 +5410,63 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E83" s="3">
         <v>3400</v>
-      </c>
-      <c r="E83" s="3">
-        <v>3200</v>
       </c>
       <c r="F83" s="3">
         <v>3200</v>
       </c>
       <c r="G83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H83" s="3">
         <v>3000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>51800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>32700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>79800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>37800</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5281,8 +5479,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5550,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5621,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5692,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5763,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,62 +5834,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E89" s="3">
         <v>41600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>24400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>44700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>60000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>38000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>37100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>49900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>233700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>69800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>126600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>238800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>120200</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5689,8 +5905,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,8 +5934,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5724,53 +5944,53 @@
         <v>-8000</v>
       </c>
       <c r="E91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-8600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7700</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-10100</v>
       </c>
       <c r="I91" s="3">
         <v>-10100</v>
       </c>
       <c r="J91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-8500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-32500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-21100</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5783,8 +6003,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6074,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,8 +6145,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5928,53 +6157,53 @@
         <v>-8000</v>
       </c>
       <c r="E94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-8600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7700</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-10100</v>
       </c>
       <c r="I94" s="3">
         <v>-10100</v>
       </c>
       <c r="J94" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-12500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-20800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-42500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>43000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-80800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-60900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-39300</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5987,8 +6216,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6245,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6039,8 +6272,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6081,8 +6314,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6385,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6456,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,62 +6527,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-30700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-27300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-58800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-67600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-247800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>18800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-179100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-46300</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6353,62 +6598,65 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>6600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6421,62 +6669,65 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E102" s="3">
         <v>5400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-27200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-67000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>43700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>27400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>27100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-61400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>105200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>64400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>33900</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6487,6 +6738,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>CCSI</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -759,65 +760,68 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>87100</v>
+      </c>
+      <c r="E8" s="3">
         <v>87000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>87800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>87500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>88100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>87800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>90600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>92800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>91500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>82400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>91800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>91100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>89300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>352700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>182100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>346800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>678500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>336800</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -830,65 +834,68 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E9" s="3">
         <v>17900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>58000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>40700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>75200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>154300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>77800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -901,8 +908,11 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -910,56 +920,56 @@
         <v>69100</v>
       </c>
       <c r="E10" s="3">
+        <v>69100</v>
+      </c>
+      <c r="F10" s="3">
         <v>70100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>70400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>71100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>71000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>73700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>75500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>73900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>66600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>76400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>75500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>74200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>294700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>141400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>271600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>524300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>259000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,65 +1012,66 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E12" s="3">
         <v>2100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>22800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>11600</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1070,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1141,8 +1158,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1185,20 +1205,20 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>24600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>29800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-17100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
@@ -1212,37 +1232,40 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E15" s="3">
         <v>5500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>4400</v>
       </c>
       <c r="I15" s="3">
         <v>4400</v>
       </c>
       <c r="J15" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="K15" s="3">
         <v>4300</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="L15" s="3">
+        <v>4300</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
@@ -1256,21 +1279,21 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3">
         <v>12300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>22300</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="3">
         <v>28700</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1283,8 +1306,11 @@
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1307,65 +1333,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E17" s="3">
         <v>53600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>49300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>47600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>50500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>52300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>51600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>54000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>57500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>45400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>59100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>50500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>50600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>177500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>149200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>258500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>424600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>219000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,65 +1405,68 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E18" s="3">
         <v>33400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>38400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>39900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>37700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>35500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>38900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>38800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>34000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>37000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>32700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>40600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>38700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>175200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>32900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>88300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>253900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>117800</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1449,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,65 +1509,66 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1600</v>
-      </c>
-      <c r="O20" s="3">
-        <v>200</v>
       </c>
       <c r="P20" s="3">
         <v>200</v>
       </c>
       <c r="Q20" s="3">
+        <v>200</v>
+      </c>
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-45800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-19100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,65 +1581,68 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E21" s="3">
         <v>40800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>41400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>45700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>46300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>34000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>47000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>43800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>37500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>34700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>39400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>46000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>42500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>227200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>49800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>121400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>287800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>136500</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,53 +1655,56 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E22" s="3">
         <v>9400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>13300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14300</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1680,8 +1720,8 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1689,65 +1729,68 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E23" s="3">
         <v>26200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>27300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>32500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>36300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>23800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>31500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>27300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>29800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>25600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>161100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>33700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>88700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>208000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>98700</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1760,65 +1803,68 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E24" s="3">
         <v>8100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>39900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>55100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>24300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1831,8 +1877,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1902,65 +1951,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E26" s="3">
         <v>18100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>23900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>26400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>24000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>21100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>15500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>15400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>121200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>74900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>152900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>74400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1973,65 +2025,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E27" s="3">
         <v>18100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>23900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>26400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>21000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>15400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>15400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>121200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>74900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>152900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>74400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2044,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2115,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2157,11 +2218,11 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2177,8 +2238,8 @@
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2186,8 +2247,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2257,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2328,65 +2395,68 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-200</v>
       </c>
       <c r="P32" s="3">
         <v>-200</v>
       </c>
       <c r="Q32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>45800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>19100</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2399,65 +2469,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E33" s="3">
         <v>18100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>23900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>26400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>21100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>15500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>15400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>109000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>74900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>152900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>74400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2541,65 +2617,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E35" s="3">
         <v>18100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>23900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>26400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>21100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>15500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>15400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>109000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>74900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>152900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>74400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,70 +2691,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2715,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2742,62 +2828,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E41" s="3">
         <v>33500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>54600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>88700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>155700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>112000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>111300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>94200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>103700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>76300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>93900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>66800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>297800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>192600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>128200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,8 +2900,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2884,62 +2974,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E43" s="3">
         <v>24900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>26300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>29700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>30800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>28000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>31100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>29900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>28800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>37600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>41300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>42200</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2955,8 +3048,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2984,8 +3080,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3026,62 +3122,65 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E45" s="3">
         <v>6700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7500</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>14300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>4900</v>
       </c>
       <c r="N45" s="3">
         <v>4900</v>
       </c>
       <c r="O45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="P45" s="3">
         <v>5400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>31900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>34600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>27800</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3097,62 +3196,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>91500</v>
+      </c>
+      <c r="E46" s="3">
         <v>74500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>89800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>84000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>98700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>125200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>192600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>155800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>155500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>136500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>139700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>111100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>128100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>96300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>367300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>268500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>198300</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,37 +3270,40 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E47" s="3">
         <v>4000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>4000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3209,21 +3314,21 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>8800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8800</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3239,62 +3344,65 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>109600</v>
+      </c>
+      <c r="E48" s="3">
         <v>106600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>103300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>98000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>93100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>88000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>82300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>75500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>68900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>62800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>54900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>50400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>46500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>41100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>101900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>101200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>115000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3310,62 +3418,65 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>388000</v>
+      </c>
+      <c r="E49" s="3">
         <v>386200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>391700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>389800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>391200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>393800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>392100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>394900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>395800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>395700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>391000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>399800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>397000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>382800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1047800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1062700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1110400</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,8 +3492,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3452,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3523,62 +3640,65 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E52" s="3">
         <v>300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>41000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>42700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>43800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>51000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>145500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>58900</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,8 +3714,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3665,62 +3788,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>629600</v>
+      </c>
+      <c r="E54" s="3">
         <v>602200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>622500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>608500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>620800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>647300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>706500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>667100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>663300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>633900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>626600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>604000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>615300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>562800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1576800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1586900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1491400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3736,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3763,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3790,62 +3920,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E57" s="3">
         <v>7400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>52900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>54300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>61700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>39500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>56600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>40200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>65000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>61800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>81000</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,46 +3992,49 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E58" s="3">
         <v>21100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2900</v>
       </c>
       <c r="J58" s="3">
         <v>2900</v>
       </c>
       <c r="K58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L58" s="3">
         <v>2800</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -3932,62 +4066,65 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E59" s="3">
         <v>21800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>27000</v>
       </c>
       <c r="G59" s="3">
         <v>27000</v>
       </c>
       <c r="H59" s="3">
+        <v>27000</v>
+      </c>
+      <c r="I59" s="3">
         <v>24300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>29300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>26500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>28300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>30100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>33900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>42700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>53500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>37800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>112800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>121800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>123600</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,62 +4140,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E60" s="3">
         <v>79300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>85300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>80400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>74200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>71400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>85100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>65000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>85500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>71300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>95600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>82200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>110100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>78000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>177800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>183500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>204700</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4074,53 +4214,56 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>589100</v>
+      </c>
+      <c r="E61" s="3">
         <v>586100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>615700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>638400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>684400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>738600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>808200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>807900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>807700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>793900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>793400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>792900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>792500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>792000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4145,62 +4288,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E62" s="3">
         <v>13500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>28200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>25500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>162300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>169600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>164200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,8 +4362,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4287,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4358,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4429,62 +4584,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>679000</v>
+      </c>
+      <c r="E66" s="3">
         <v>681700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>715700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>732900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>772600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>823400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>905800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>884500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>904000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>889200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>918900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>903200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>929300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>895500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>340100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>353100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>368900</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4527,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4598,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4669,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4740,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4811,53 +4982,56 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-62500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-83700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-101700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-122900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-146700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-173100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-189900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-213900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-235000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-250400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-267000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-280400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-302100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-318900</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4873,8 +5047,8 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X72" s="3">
         <v>0</v>
@@ -4882,8 +5056,11 @@
       <c r="Y72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4953,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5024,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5095,62 +5278,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-79500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-93200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-124400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-151800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-176100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-199300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-217400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-240700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-255300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-292300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-299200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-313900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-332700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1236700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1233700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1122500</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5166,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5237,70 +5426,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5313,65 +5505,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E81" s="3">
         <v>18100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>23900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>26400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>21100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>15500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>15400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>109000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>74900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>152900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>74400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5384,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5411,65 +5609,66 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E83" s="3">
         <v>3300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>3200</v>
       </c>
       <c r="G83" s="3">
         <v>3200</v>
       </c>
       <c r="H83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I83" s="3">
         <v>3000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>51800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>32700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>79800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>37800</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5482,8 +5681,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5553,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5624,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5695,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5766,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5837,65 +6051,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E89" s="3">
         <v>11100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>41600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>24400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>44700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>60000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>38000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>37100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>49900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>233700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>69800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>126600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>238800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>120200</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5908,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5935,65 +6155,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-8000</v>
+        <v>-7200</v>
       </c>
       <c r="E91" s="3">
         <v>-8000</v>
       </c>
       <c r="F91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-8600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7700</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-10100</v>
       </c>
       <c r="J91" s="3">
         <v>-10100</v>
       </c>
       <c r="K91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-8500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-10300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-32500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-21100</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6006,8 +6227,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6077,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6148,65 +6375,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8000</v>
+        <v>-12200</v>
       </c>
       <c r="E94" s="3">
         <v>-8000</v>
       </c>
       <c r="F94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="G94" s="3">
         <v>-8600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7700</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-10100</v>
       </c>
       <c r="J94" s="3">
         <v>-10100</v>
       </c>
       <c r="K94" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="L94" s="3">
         <v>-12500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-42500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>43000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-80800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-60900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-39300</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6219,8 +6449,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6246,8 +6479,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6275,8 +6509,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6317,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6388,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6459,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6530,65 +6773,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-21800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-27300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-58800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-67600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-247800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>18800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-179100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-46300</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6601,65 +6847,68 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E101" s="3">
         <v>6300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>7300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>6600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6672,65 +6921,68 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-67000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>43700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>17100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>27400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>27100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-61400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>105200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>64400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>33900</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6741,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
   <si>
     <t>CCSI</t>
   </si>
@@ -656,101 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -763,68 +764,71 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>87700</v>
+      </c>
+      <c r="E8" s="3">
         <v>87100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>87000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>87800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>87500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>88100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>87800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>90600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>92800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>91500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>82400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>91800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>91100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>89300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>352700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>182100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>346800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>678500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>336800</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -837,68 +841,71 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E9" s="3">
         <v>18100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>58000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>40700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>75200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>154300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>77800</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -911,68 +918,71 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>69100</v>
+        <v>70100</v>
       </c>
       <c r="E10" s="3">
         <v>69100</v>
       </c>
       <c r="F10" s="3">
+        <v>69100</v>
+      </c>
+      <c r="G10" s="3">
         <v>70100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>70400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>71100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>71000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>73700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>75500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>73900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>66600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>76400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>75500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>74200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>294700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>141400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>271600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>524300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>259000</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -985,8 +995,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1013,8 +1026,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,59 +1036,59 @@
         <v>1700</v>
       </c>
       <c r="E12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F12" s="3">
         <v>2100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>22800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>11600</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,8 +1101,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1161,8 +1178,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1208,20 +1228,20 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>24600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>29800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-17100</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
@@ -1235,40 +1255,43 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E15" s="3">
         <v>5200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>4400</v>
       </c>
       <c r="J15" s="3">
         <v>4400</v>
       </c>
       <c r="K15" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="L15" s="3">
         <v>4300</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>4300</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
@@ -1282,21 +1305,21 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3">
         <v>12300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>22300</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" s="3">
         <v>28700</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1309,8 +1332,11 @@
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,68 +1360,69 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E17" s="3">
         <v>49600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>53600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>49300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>47600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>50500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>52300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>51600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>57500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>45400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>59100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>50500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>50600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>177500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>149200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>258500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>424600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>219000</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1408,68 +1435,71 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E18" s="3">
         <v>37500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>33400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>38400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>39900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>37700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>35500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>38900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>38800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>37000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>40600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>38700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>175200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>32900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>88300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>253900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>117800</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,8 +1512,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1510,68 +1543,69 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1600</v>
-      </c>
-      <c r="P20" s="3">
-        <v>200</v>
       </c>
       <c r="Q20" s="3">
         <v>200</v>
       </c>
       <c r="R20" s="3">
+        <v>200</v>
+      </c>
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-45800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-19100</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,68 +1618,71 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E21" s="3">
         <v>41600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>41400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>45700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>46300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>34000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>47000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>43800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>37500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>34700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>39400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>46000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>42500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>227200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>49800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>121400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>287800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>136500</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,56 +1695,59 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E22" s="3">
         <v>9000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>13300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>14300</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1723,8 +1763,8 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1732,68 +1772,71 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E23" s="3">
         <v>27900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>26200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>27300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>32500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>36300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>27300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>20600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>18900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>29800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>25600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>161100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>33700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>88700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>208000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>98700</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1806,68 +1849,71 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E24" s="3">
         <v>6700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>39900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>13800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>55100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>24300</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1880,8 +1926,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,68 +2003,71 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E26" s="3">
         <v>21200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>18100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>21100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>26400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>24000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>21100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>15500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>21900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>121200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>27200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>74900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>152900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>74400</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2028,68 +2080,71 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E27" s="3">
         <v>21200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>26400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>21000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>15400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>15400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>21900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>121200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>74900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>152900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>74400</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2102,8 +2157,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2234,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2221,11 +2282,11 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-12200</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2241,8 +2302,8 @@
       <c r="W29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2250,8 +2311,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2388,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,68 +2465,71 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-200</v>
       </c>
       <c r="Q32" s="3">
         <v>-200</v>
       </c>
       <c r="R32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>45800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>19100</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2472,68 +2542,71 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E33" s="3">
         <v>21200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>18100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>26400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>24000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>21100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>15500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>15400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>21900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>109000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>27200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>74900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>152900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>74400</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,8 +2619,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,68 +2696,71 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E35" s="3">
         <v>21200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>18100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>26400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>24000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>21100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>15500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>15400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>21900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>109000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>27200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>74900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>152900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>74400</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,73 +2773,76 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2855,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2886,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,65 +2915,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E41" s="3">
         <v>53400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>54600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>61500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>88700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>155700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>112000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>111300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>94200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>103700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>76300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>93900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>66800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>297800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>192600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>128200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2903,8 +2990,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2977,65 +3067,68 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E43" s="3">
         <v>26700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>30800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>31100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>28800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>37600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>41300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>42200</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3051,8 +3144,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3083,8 +3179,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3125,65 +3221,68 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E45" s="3">
         <v>5700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7500</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>14300</v>
-      </c>
-      <c r="N45" s="3">
-        <v>4900</v>
       </c>
       <c r="O45" s="3">
         <v>4900</v>
       </c>
       <c r="P45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="Q45" s="3">
         <v>5400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>31900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>34600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>27800</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,65 +3298,68 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E46" s="3">
         <v>91500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>74500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>89800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>84000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>98700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>125200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>192600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>155800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>155500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>136500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>139700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>111100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>128100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>96300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>367300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>268500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>198300</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3273,8 +3375,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3282,31 +3387,31 @@
         <v>8000</v>
       </c>
       <c r="E47" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F47" s="3">
         <v>4000</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>4000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3317,21 +3422,21 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>8800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8800</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,65 +3452,68 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>113800</v>
+      </c>
+      <c r="E48" s="3">
         <v>109600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>106600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>103300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>98000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>93100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>88000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>82300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>75500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>68900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>62800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>54900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>50400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>46500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>41100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>101900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>101200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>115000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3421,65 +3529,68 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>392800</v>
+      </c>
+      <c r="E49" s="3">
         <v>388000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>386200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>391700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>389800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>391200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>393800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>392100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>394900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>395800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>395700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>391000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>399800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>397000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>382800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1047800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1062700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1110400</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3495,8 +3606,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3683,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,65 +3760,68 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>41000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>42700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>43800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>42700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>51000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>145500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>58900</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3837,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,65 +3914,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>641500</v>
+      </c>
+      <c r="E54" s="3">
         <v>629600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>602200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>622500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>608500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>620800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>647300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>706500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>667100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>663300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>633900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>626600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>604000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>615300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>562800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1576800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1586900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1491400</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3991,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4022,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,65 +4051,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>52900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>54300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>61700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>39500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>56600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>40200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>65000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>61800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>81000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,49 +4126,52 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E58" s="3">
         <v>8400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10600</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2900</v>
       </c>
       <c r="K58" s="3">
         <v>2900</v>
       </c>
       <c r="L58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M58" s="3">
         <v>2800</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4069,65 +4203,68 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E59" s="3">
         <v>25000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>26200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>27000</v>
       </c>
       <c r="H59" s="3">
         <v>27000</v>
       </c>
       <c r="I59" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J59" s="3">
         <v>24300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>29300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>26500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>28300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>30100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>33900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>42700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>53500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>37800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>112800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>121800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>123600</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4143,65 +4280,68 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E60" s="3">
         <v>73300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>79300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>85300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>80400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>74200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>71400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>85100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>65000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>85500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>71300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>95600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>82200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>110100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>78000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>177800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>183500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>204700</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4357,11 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4226,47 +4369,47 @@
         <v>589100</v>
       </c>
       <c r="E61" s="3">
+        <v>589100</v>
+      </c>
+      <c r="F61" s="3">
         <v>586100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>615700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>638400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>684400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>738600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>808200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>807900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>807700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>793900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>793400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>792900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>792500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>792000</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4291,65 +4434,68 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E62" s="3">
         <v>13900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>12100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>29900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>28200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>26700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>25500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>162300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>169600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>164200</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4365,8 +4511,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4588,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4665,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,65 +4742,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>668000</v>
+      </c>
+      <c r="E66" s="3">
         <v>679000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>681700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>715700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>732900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>772600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>823400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>905800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>884500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>904000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>889200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>918900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>903200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>929300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>895500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>340100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>353100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>368900</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,8 +4819,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +4850,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +4925,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,8 +5002,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4911,8 +5079,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,56 +5156,59 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-62500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-83700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-101700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-122900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-146700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-173100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-189900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-213900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-235000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-250400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-267000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-280400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-302100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-318900</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5050,8 +5224,8 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y72" s="3">
         <v>0</v>
@@ -5059,8 +5233,11 @@
       <c r="Z72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5310,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5387,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,65 +5464,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-49400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-79500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-93200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-124400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-151800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-176100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-199300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-217400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-240700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-255300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-292300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-299200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-313900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-332700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1236700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1233700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1122500</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5355,8 +5541,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,73 +5618,76 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5508,68 +5700,71 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E81" s="3">
         <v>21200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>18100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>26400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>24000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>21100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>15500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>15400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>21900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>109000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>27200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>74900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>152900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>74400</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5582,8 +5777,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,68 +5808,69 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E83" s="3">
         <v>3900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>3200</v>
       </c>
       <c r="H83" s="3">
         <v>3200</v>
       </c>
       <c r="I83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J83" s="3">
         <v>3000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>51800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>16100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>32700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>79800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>37800</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5684,8 +5883,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +5960,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6037,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6114,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6191,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,68 +6268,71 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E89" s="3">
         <v>40900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>41600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>44700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>60000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>38000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>37100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>49900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>233700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>69800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>126600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>238800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>120200</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6128,8 +6345,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,68 +6376,69 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7200</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-8000</v>
       </c>
       <c r="F91" s="3">
         <v>-8000</v>
       </c>
       <c r="G91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="H91" s="3">
         <v>-8600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7700</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-10100</v>
       </c>
       <c r="K91" s="3">
         <v>-10100</v>
       </c>
       <c r="L91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-8500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-32500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-21100</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6230,8 +6451,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6528,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,68 +6605,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12200</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-8000</v>
       </c>
       <c r="F94" s="3">
         <v>-8000</v>
       </c>
       <c r="G94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="H94" s="3">
         <v>-8600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7700</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-10100</v>
       </c>
       <c r="K94" s="3">
         <v>-10100</v>
       </c>
       <c r="L94" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="M94" s="3">
         <v>-12500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-42500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>43000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-80800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-60900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-39300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6452,8 +6682,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,8 +6713,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6512,8 +6746,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6554,8 +6788,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +6865,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +6942,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,68 +7019,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-21800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-27300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-58800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-67600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-247800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>18800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-179100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-46300</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6850,68 +7096,71 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>7300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>7300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>6600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6924,68 +7173,71 @@
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E102" s="3">
         <v>19900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-12300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-27200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-67000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>43700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>17100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>27400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>27100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-61400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>105200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>64400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>33900</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6996,6 +7248,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
   <si>
     <t>CCSI</t>
   </si>
@@ -656,109 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -771,74 +771,77 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>87100</v>
+      </c>
+      <c r="E8" s="3">
         <v>87800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>87700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>87100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>87000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>87800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>87500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>88100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>87800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>90600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>92800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>91500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>82400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>91800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>91100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>89300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>352700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>182100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>346800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>678500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>336800</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -851,74 +854,77 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E9" s="3">
         <v>17500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>58000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>40700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>75200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>154300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>77800</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -931,74 +937,77 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E10" s="3">
         <v>70200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>70100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>69100</v>
       </c>
       <c r="G10" s="3">
         <v>69100</v>
       </c>
       <c r="H10" s="3">
+        <v>69100</v>
+      </c>
+      <c r="I10" s="3">
         <v>70100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>70400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>71100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>71000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>73700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>75500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>73900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>66600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>76400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>75500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>74200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>294700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>141400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>271600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>524300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>259000</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1011,8 +1020,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,74 +1053,75 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E12" s="3">
         <v>2000</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1700</v>
       </c>
       <c r="F12" s="3">
         <v>1700</v>
       </c>
       <c r="G12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H12" s="3">
         <v>2100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>22800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>11600</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,8 +1134,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,8 +1217,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1254,20 +1273,20 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>24600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>29800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-17100</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
@@ -1281,8 +1300,11 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1290,37 +1312,37 @@
         <v>4500</v>
       </c>
       <c r="E15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F15" s="3">
         <v>4600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>4400</v>
       </c>
       <c r="L15" s="3">
         <v>4400</v>
       </c>
       <c r="M15" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="N15" s="3">
         <v>4300</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>4300</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
@@ -1334,21 +1356,21 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="3">
         <v>12300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>22300</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X15" s="3">
         <v>28700</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1361,8 +1383,11 @@
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1388,74 +1413,75 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E17" s="3">
         <v>49800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>49600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>53600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>49300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>47600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>50500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>52300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>51600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>54000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>57500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>45400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>59100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>50500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>50600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>177500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>149200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>258500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>424600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>219000</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1468,74 +1494,77 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E18" s="3">
         <v>37900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>37500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>33400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>38400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>39900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>37700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>35500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>38900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>38800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>34000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>37000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>32700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>40600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>38700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>175200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>32900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>88300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>253900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>117800</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,8 +1577,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,8 +1610,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1587,65 +1620,65 @@
         <v>-100</v>
       </c>
       <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>2300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1600</v>
-      </c>
-      <c r="R20" s="3">
-        <v>200</v>
       </c>
       <c r="S20" s="3">
         <v>200</v>
       </c>
       <c r="T20" s="3">
+        <v>200</v>
+      </c>
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-45800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-19100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,74 +1691,77 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E21" s="3">
         <v>42600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>41300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>41600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>40800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>41400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>45700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>46300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>34000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>47000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>43800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>37500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>34700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>39400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>46000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>42500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>227200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>49800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>121400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>287800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>136500</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,62 +1774,65 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E22" s="3">
         <v>8800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>13900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>14300</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,8 +1848,8 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -1818,74 +1857,77 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E23" s="3">
         <v>30000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>28500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>27900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>26200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>27300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>32500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>36300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>31500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>27300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>18900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>21700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>29800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>25600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>161100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>88700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>208000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>98700</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1898,74 +1940,77 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E24" s="3">
         <v>7900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>39900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>55100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>24300</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,8 +2023,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,74 +2106,77 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E26" s="3">
         <v>22100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>20800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>21200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>23900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>26400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>15400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>21900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>18500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>121200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>27200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>74900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>152900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>74400</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2138,74 +2189,77 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E27" s="3">
         <v>22100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>20800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>23900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>26400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>24000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>15400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>15400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>21900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>121200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>27200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>74900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>152900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>74400</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2218,8 +2272,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2298,8 +2355,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2349,11 +2409,11 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>-12200</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2369,8 +2429,8 @@
       <c r="Y29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -2378,8 +2438,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2458,8 +2521,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2538,8 +2604,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2547,65 +2616,65 @@
         <v>100</v>
       </c>
       <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-200</v>
       </c>
       <c r="S32" s="3">
         <v>-200</v>
       </c>
       <c r="T32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>45800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>19100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2618,74 +2687,77 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E33" s="3">
         <v>22100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>20800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>23900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>24000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>15500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>15400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>21900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>109000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>74900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>152900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>74400</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2698,8 +2770,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2778,74 +2853,77 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E35" s="3">
         <v>22100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>20800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>23900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>24000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>15500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>15400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>21900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>109000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>74900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>152900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>74400</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,79 +2936,82 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2943,8 +3024,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2973,8 +3057,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3003,71 +3088,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E41" s="3">
         <v>97600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>57900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>53400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>54600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>61500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>88700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>155700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>111300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>94200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>103700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>76300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>93900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>66800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>297800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>192600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>128200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,8 +3169,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3163,71 +3252,74 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E43" s="3">
         <v>24200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>26700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>25800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>27400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>26300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>30800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>29600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>28000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>31100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>29900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>28800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>24800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>37600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>41300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>42200</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3243,8 +3335,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3281,8 +3376,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3323,71 +3418,74 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E45" s="3">
         <v>3300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7500</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>14300</v>
-      </c>
-      <c r="P45" s="3">
-        <v>4900</v>
       </c>
       <c r="Q45" s="3">
         <v>4900</v>
       </c>
       <c r="R45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="S45" s="3">
         <v>5400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>31900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>34600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>27800</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3403,71 +3501,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>117200</v>
+      </c>
+      <c r="E46" s="3">
         <v>128200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>92400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>91500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>74500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>89800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>84000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>98700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>125200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>192600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>155800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>155500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>136500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>139700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>111100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>128100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>96300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>367300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>268500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>198300</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,8 +3584,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3498,31 +3602,31 @@
         <v>8000</v>
       </c>
       <c r="G47" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H47" s="3">
         <v>4000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>4000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3533,21 +3637,21 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3">
         <v>8800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3563,71 +3667,74 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E48" s="3">
         <v>118000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>113800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>109600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>106600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>103300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>98000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>93100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>88000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>82300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>75500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>68900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>62800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>54900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>50400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>46500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>41100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>101900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>101200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>115000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,71 +3750,74 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>391700</v>
+      </c>
+      <c r="E49" s="3">
         <v>392100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>392800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>388000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>386200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>391700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>389800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>391200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>393800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>392100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>394900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>395800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>395700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>391000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>399800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>397000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>382800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1047800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1062700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1110400</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,8 +3833,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3803,8 +3916,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,8 +3999,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3892,62 +4011,62 @@
         <v>3300</v>
       </c>
       <c r="E52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F52" s="3">
         <v>1700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>38800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>41000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>42700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>43800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>42700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>51000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>145500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>58900</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3963,8 +4082,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4043,71 +4165,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>663800</v>
+      </c>
+      <c r="E54" s="3">
         <v>675000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>641500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>629600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>602200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>622500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>608500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>620800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>647300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>706500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>667100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>663300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>633900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>626600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>604000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>615300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>562800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1576800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1586900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1491400</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4248,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4153,8 +4281,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4183,71 +4312,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E57" s="3">
         <v>6600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>52900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>35500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>54300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>41200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>61700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>39500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>56600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>40200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>65000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>61800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>81000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4263,55 +4393,58 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E58" s="3">
         <v>2600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>18600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10600</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2900</v>
       </c>
       <c r="M58" s="3">
         <v>2900</v>
       </c>
       <c r="N58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="O58" s="3">
         <v>2800</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4343,71 +4476,74 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E59" s="3">
         <v>23200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>27000</v>
       </c>
       <c r="J59" s="3">
         <v>27000</v>
       </c>
       <c r="K59" s="3">
+        <v>27000</v>
+      </c>
+      <c r="L59" s="3">
         <v>24300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>29300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>26500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>28300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>30100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>33900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>42700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>53500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>37800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>112800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>121800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>123600</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,71 +4559,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E60" s="3">
         <v>69700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>61900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>73300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>79300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>85300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>80400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>74200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>71400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>85100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>65000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>85500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>71300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>95600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>82200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>110100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>78000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>177800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>183500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>204700</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,62 +4642,65 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>561100</v>
+      </c>
+      <c r="E61" s="3">
         <v>588900</v>
-      </c>
-      <c r="E61" s="3">
-        <v>589100</v>
       </c>
       <c r="F61" s="3">
         <v>589100</v>
       </c>
       <c r="G61" s="3">
+        <v>589100</v>
+      </c>
+      <c r="H61" s="3">
         <v>586100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>615700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>638400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>684400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>738600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>808200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>807900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>807700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>793900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>793400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>792900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>792500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>792000</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4583,71 +4725,74 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E62" s="3">
         <v>14600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>29900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>28200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>26700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>25500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>162300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>169600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>164200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4808,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4743,8 +4891,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4823,8 +4974,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4903,71 +5057,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>650000</v>
+      </c>
+      <c r="E66" s="3">
         <v>677600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>668000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>679000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>681700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>715700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>732900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>772600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>823400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>905800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>884500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>904000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>889200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>918900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>903200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>929300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>895500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>340100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>353100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>368900</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,8 +5140,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5013,8 +5173,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5093,8 +5254,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5173,8 +5337,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5253,8 +5420,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5333,62 +5503,65 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-19700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-41700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-62500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-83700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-101700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-122900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-146700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-173100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-189900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-213900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-235000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-250400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-267000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-280400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-302100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-318900</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5404,8 +5577,8 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA72" s="3">
         <v>0</v>
@@ -5413,8 +5586,11 @@
       <c r="AB72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5493,8 +5669,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5573,8 +5752,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5653,71 +5835,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-26500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-49400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-79500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-93200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-124400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-151800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-176100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-199300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-217400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-240700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-255300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-292300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-299200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-313900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-332700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1236700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1233700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1122500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5733,8 +5918,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5813,79 +6001,82 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5898,74 +6089,77 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E81" s="3">
         <v>22100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>20800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>23900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>24000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>15500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>15400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>21900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>109000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>74900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>152900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>74400</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,8 +6172,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6008,74 +6205,75 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E83" s="3">
         <v>4000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>3200</v>
       </c>
       <c r="J83" s="3">
         <v>3200</v>
       </c>
       <c r="K83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L83" s="3">
         <v>3000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>51800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>16100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>32700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>79800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>37800</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6088,8 +6286,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6168,8 +6369,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6248,8 +6452,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6328,8 +6535,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6408,8 +6618,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6488,74 +6701,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E89" s="3">
         <v>51600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>28300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>40900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>41600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>44700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>60000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>38000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>37100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>49900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>233700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>69800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>126600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>238800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>120200</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6568,8 +6784,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6598,74 +6817,75 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-8000</v>
       </c>
       <c r="H91" s="3">
         <v>-8000</v>
       </c>
       <c r="I91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J91" s="3">
         <v>-8600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7700</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-10100</v>
       </c>
       <c r="M91" s="3">
         <v>-10100</v>
       </c>
       <c r="N91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-8500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-19500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-32500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-21100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6678,8 +6898,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6758,8 +6981,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6838,74 +7064,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-8000</v>
       </c>
       <c r="H94" s="3">
         <v>-8000</v>
       </c>
       <c r="I94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-8600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7700</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-10100</v>
       </c>
       <c r="M94" s="3">
         <v>-10100</v>
       </c>
       <c r="N94" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="O94" s="3">
         <v>-12500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-42500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>43000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-80800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-60900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-39300</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6918,8 +7147,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6948,8 +7180,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6986,8 +7219,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7028,8 +7261,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7108,8 +7344,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7188,8 +7427,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7268,74 +7510,77 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-18500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-21800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-30700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-27300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-58800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-67600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-7400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-247800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>18800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-179100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-46300</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7348,74 +7593,77 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E101" s="3">
         <v>2500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>7300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>6600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-600</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7428,74 +7676,77 @@
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E102" s="3">
         <v>39800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-67000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>43700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>27400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>27100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-61400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>105200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>64400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>33900</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7506,6 +7757,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCSI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>CCSI</t>
   </si>
@@ -656,112 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -774,77 +775,80 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E8" s="3">
         <v>87100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>87800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>87700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>87100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>87000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>87800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>87500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>88100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>87800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>90600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>92800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>91500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>82400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>91800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>91100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>89300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>352700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>182100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>346800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>678500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>336800</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -857,77 +861,80 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E9" s="3">
         <v>17400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>17500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>58000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>40700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>75200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>154300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>77800</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -940,77 +947,80 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E10" s="3">
         <v>69700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>70200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>70100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>69100</v>
       </c>
       <c r="H10" s="3">
         <v>69100</v>
       </c>
       <c r="I10" s="3">
+        <v>69100</v>
+      </c>
+      <c r="J10" s="3">
         <v>70100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>70400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>71100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>71000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>73700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>75500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>73900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>66600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>76400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>75500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>74200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>294700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>141400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>271600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>524300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>259000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,8 +1033,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1054,77 +1067,78 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
         <v>2100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1700</v>
       </c>
       <c r="G12" s="3">
         <v>1700</v>
       </c>
       <c r="H12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I12" s="3">
         <v>2100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>8300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>22800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>11600</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1137,8 +1151,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1220,8 +1237,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1276,20 +1296,20 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>24600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>29800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-17100</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
@@ -1303,49 +1323,52 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>4500</v>
+        <v>4900</v>
       </c>
       <c r="E15" s="3">
         <v>4500</v>
       </c>
       <c r="F15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G15" s="3">
         <v>4600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4800</v>
-      </c>
-      <c r="L15" s="3">
-        <v>4400</v>
       </c>
       <c r="M15" s="3">
         <v>4400</v>
       </c>
       <c r="N15" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="O15" s="3">
         <v>4300</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>4300</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
@@ -1359,21 +1382,21 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" s="3">
         <v>12300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>22300</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="3">
         <v>28700</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1386,8 +1409,11 @@
       <c r="AC15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1414,77 +1440,78 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E17" s="3">
         <v>51300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>49800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>49600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>53600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>49300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>47600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>50500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>52300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>51600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>54000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>57500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>45400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>59100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>50500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>50600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>177500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>149200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>258500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>424600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>219000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1497,77 +1524,80 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E18" s="3">
         <v>35800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>37900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>39000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>37500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>33400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>38400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>39900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>37700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>35500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>38900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>38800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>34000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>37000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>32700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>40600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>38700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>175200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>32900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>88300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>253900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>117800</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1610,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1611,77 +1644,78 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-100</v>
+        <v>-1400</v>
       </c>
       <c r="E20" s="3">
         <v>-100</v>
       </c>
       <c r="F20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G20" s="3">
         <v>2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1600</v>
-      </c>
-      <c r="S20" s="3">
-        <v>200</v>
       </c>
       <c r="T20" s="3">
         <v>200</v>
       </c>
       <c r="U20" s="3">
+        <v>200</v>
+      </c>
+      <c r="V20" s="3">
         <v>900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-45800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-19100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1694,77 +1728,80 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>44100</v>
+      </c>
+      <c r="E21" s="3">
         <v>40300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>42600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>41300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>41600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>40800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>41400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>45700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>46300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>34000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>47000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>43800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>37500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>34700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>39400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>46000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>42500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>227200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>49800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>121400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>287800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>136500</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1777,65 +1814,68 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E22" s="3">
         <v>9000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>13300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>14300</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1851,8 +1891,8 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1860,77 +1900,80 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E23" s="3">
         <v>27600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>28500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>27900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>26200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>27300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>32500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>36300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>27300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>20600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>18900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>21700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>29800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>25600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>161100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>33700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>88700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>208000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>98700</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1943,77 +1986,80 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E24" s="3">
         <v>7100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>39900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>13800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>55100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>24300</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2026,8 +2072,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2109,77 +2158,80 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E26" s="3">
         <v>20500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>20800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>23900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>26400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>15500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>15400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>21900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>18500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>121200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>27200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>74900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>152900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>74400</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,77 +2244,80 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E27" s="3">
         <v>20500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>20800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>18100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>23900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>26400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>24000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>15400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>15400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>21900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>121200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>74900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>152900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>74400</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,8 +2330,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2358,8 +2416,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2412,11 +2473,11 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-12200</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
@@ -2432,8 +2493,8 @@
       <c r="Z29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -2441,8 +2502,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2524,8 +2588,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2607,77 +2674,80 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>100</v>
+        <v>1400</v>
       </c>
       <c r="E32" s="3">
         <v>100</v>
       </c>
       <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-200</v>
       </c>
       <c r="T32" s="3">
         <v>-200</v>
       </c>
       <c r="U32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V32" s="3">
         <v>-900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>45800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>19100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,77 +2760,80 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E33" s="3">
         <v>20500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>20800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>23900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>26400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>24000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>15500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>15400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>21900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>109000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>74900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>152900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>74400</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2846,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2856,77 +2932,80 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E35" s="3">
         <v>20500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>20800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>23900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>26400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>24000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>15500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>15400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>21900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>109000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>74900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>152900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>74400</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2939,82 +3018,85 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3109,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3058,8 +3143,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3089,74 +3175,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E41" s="3">
         <v>74700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>97600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>57900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>53400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>54600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>61500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>88700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>155700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>112000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>111300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>94200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>103700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>76300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>93900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>66800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>297800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>192600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>128200</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3172,8 +3259,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3255,74 +3345,77 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E43" s="3">
         <v>23700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>26700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>26100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>27400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>26300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>30800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>28000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>31100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>29900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>28800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>24800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>37600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>41300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>42200</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3338,8 +3431,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3379,8 +3475,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3421,74 +3517,77 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E45" s="3">
         <v>9800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7500</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>14300</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>4900</v>
       </c>
       <c r="R45" s="3">
         <v>4900</v>
       </c>
       <c r="S45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="T45" s="3">
         <v>5400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>31900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>34600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>27800</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,74 +3603,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>130200</v>
+      </c>
+      <c r="E46" s="3">
         <v>117200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>128200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>92400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>91500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>74500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>89800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>84000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>98700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>125200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>192600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>155800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>155500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>136500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>139700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>111100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>128100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>96300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>367300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>268500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>198300</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,8 +3689,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3605,31 +3710,31 @@
         <v>8000</v>
       </c>
       <c r="H47" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I47" s="3">
         <v>4000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>4000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3640,21 +3745,21 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>8800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8800</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3670,74 +3775,77 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>125500</v>
+      </c>
+      <c r="E48" s="3">
         <v>122000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>118000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>113800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>109600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>106600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>103300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>98000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>93100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>88000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>82300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>75500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>68900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>62800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>54900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>50400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>46500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>41100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>101900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>101200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>115000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3753,74 +3861,77 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>389500</v>
+      </c>
+      <c r="E49" s="3">
         <v>391700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>392100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>392800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>388000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>386200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>391700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>389800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>391200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>393800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>392100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>394900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>395800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>395700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>391000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>399800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>397000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>382800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1047800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1062700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1110400</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3836,8 +3947,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3919,8 +4033,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4002,74 +4119,77 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3300</v>
+        <v>4300</v>
       </c>
       <c r="E52" s="3">
         <v>3300</v>
       </c>
       <c r="F52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G52" s="3">
         <v>1700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>38800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>41000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>42700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>43800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>42700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>51000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>145500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>58900</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4085,8 +4205,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4168,74 +4291,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>678700</v>
+      </c>
+      <c r="E54" s="3">
         <v>663800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>675000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>641500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>629600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>602200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>622500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>608500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>620800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>647300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>706500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>667100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>663300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>633900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>626600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>604000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>615300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>562800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1576800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1586900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1491400</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4251,8 +4377,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4282,8 +4411,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4313,74 +4443,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E57" s="3">
         <v>7500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>52900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>35500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>54300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>41200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>61700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>39500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>56600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>40200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>65000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>61800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>81000</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,8 +4527,11 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4405,49 +4539,49 @@
         <v>9600</v>
       </c>
       <c r="E58" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F58" s="3">
         <v>2600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>18600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10600</v>
-      </c>
-      <c r="M58" s="3">
-        <v>2900</v>
       </c>
       <c r="N58" s="3">
         <v>2900</v>
       </c>
       <c r="O58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P58" s="3">
         <v>2800</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -4479,74 +4613,77 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E59" s="3">
         <v>19900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>27000</v>
       </c>
       <c r="K59" s="3">
         <v>27000</v>
       </c>
       <c r="L59" s="3">
+        <v>27000</v>
+      </c>
+      <c r="M59" s="3">
         <v>24300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>29300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>26500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>30100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>33900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>42700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>53500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>37800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>112800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>121800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>123600</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4562,74 +4699,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E60" s="3">
         <v>65500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>69700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>61900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>73300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>79300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>85300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>80400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>74200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>71400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>85100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>65000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>85500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>71300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>95600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>82200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>110100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>78000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>177800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>183500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>204700</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4645,65 +4785,68 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>558900</v>
+      </c>
+      <c r="E61" s="3">
         <v>561100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>588900</v>
-      </c>
-      <c r="F61" s="3">
-        <v>589100</v>
       </c>
       <c r="G61" s="3">
         <v>589100</v>
       </c>
       <c r="H61" s="3">
+        <v>589100</v>
+      </c>
+      <c r="I61" s="3">
         <v>586100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>615700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>638400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>684400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>738600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>808200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>807900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>807700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>793900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>793400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>792900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>792500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>792000</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4728,74 +4871,77 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E62" s="3">
         <v>14700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>29900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>28200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>26700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>25500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>162300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>169600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>164200</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4811,8 +4957,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4894,8 +5043,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4977,8 +5129,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5060,74 +5215,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>656700</v>
+      </c>
+      <c r="E66" s="3">
         <v>650000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>677600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>668000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>679000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>681700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>715700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>732900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>772600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>823400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>905800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>884500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>904000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>889200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>918900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>903200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>929300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>895500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>340100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>353100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>368900</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5143,8 +5301,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5174,8 +5335,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5257,8 +5419,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5340,8 +5505,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5423,8 +5591,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5506,65 +5677,68 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E72" s="3">
         <v>800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-19700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-41700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-62500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-83700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-101700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-122900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-146700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-173100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-189900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-213900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-235000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-250400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-267000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-280400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-302100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-318900</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5580,8 +5754,8 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA72" s="3">
-        <v>0</v>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB72" s="3">
         <v>0</v>
@@ -5589,8 +5763,11 @@
       <c r="AC72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5672,8 +5849,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5755,8 +5935,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5838,74 +6021,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-2600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-26500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-49400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-79500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-93200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-124400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-151800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-176100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-199300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-217400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-240700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-255300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-292300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-299200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-313900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-332700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1236700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1233700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1122500</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5921,8 +6107,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6004,82 +6193,85 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6092,77 +6284,80 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E81" s="3">
         <v>20500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>20800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>23900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>26400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>24000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>15500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>15400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>21900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>109000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>74900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>152900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>74400</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6175,8 +6370,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6206,77 +6404,78 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E83" s="3">
         <v>4600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3200</v>
       </c>
       <c r="K83" s="3">
         <v>3200</v>
       </c>
       <c r="L83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M83" s="3">
         <v>3000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>51800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>16100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>32700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>79800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>37800</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6289,8 +6488,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6372,8 +6574,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6455,8 +6660,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6538,8 +6746,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6621,8 +6832,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6704,77 +6918,80 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E89" s="3">
         <v>15200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>51600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>28300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>40900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>41600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>44700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>60000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>38000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>37100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>49900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>233700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>69800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>126600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>238800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>120200</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6787,8 +7004,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6818,77 +7038,78 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-8000</v>
       </c>
       <c r="I91" s="3">
         <v>-8000</v>
       </c>
       <c r="J91" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-8600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7700</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-10100</v>
       </c>
       <c r="N91" s="3">
         <v>-10100</v>
       </c>
       <c r="O91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-8500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-32500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-21100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6901,8 +7122,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6984,8 +7208,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7067,77 +7294,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12200</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-8000</v>
       </c>
       <c r="I94" s="3">
         <v>-8000</v>
       </c>
       <c r="J94" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-8600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7700</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-10100</v>
       </c>
       <c r="N94" s="3">
         <v>-10100</v>
       </c>
       <c r="O94" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-12500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-20800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-42500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>43000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-80800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-60900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-39300</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7150,8 +7380,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7181,8 +7414,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7222,8 +7456,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7264,8 +7498,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7347,8 +7584,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7430,8 +7670,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7513,77 +7756,80 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-30200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-30700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-27300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-58800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-67600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-247800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>18800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-179100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-46300</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7596,77 +7842,80 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>7300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>7300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>6600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-600</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7679,77 +7928,80 @@
       <c r="AC101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-23000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>39800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-27200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-67000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>43700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>27400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>27100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-61400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>105200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>64400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>33900</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7760,6 +8012,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
